--- a/questforge/datasets/pipeline_run_review_20260423_fullcheck_v3/dataset.xlsx
+++ b/questforge/datasets/pipeline_run_review_20260423_fullcheck_v3/dataset.xlsx
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-23T13:22:16+08:00</t>
+          <t>2026-04-23T20:43:07+08:00</t>
         </is>
       </c>
     </row>
